--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409539&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409538&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409537&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409536&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -583,88 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409535&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409534&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
+        <v>ששון שאולוב - המונית העצובה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409551&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
+        <v>ששון שאולוב - המונית העצובה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
+        <v>רומי קוגן - מסיבה של מחשבות</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409550&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
+        <v>רומי קוגן - מסיבה של מחשבות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
+        <v>משה כורסיה - עומד מולך היום</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409549&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
+        <v>משה כורסיה - עומד מולך היום</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
+        <v>יהודה בוחבוט - אלף גלגולים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409548&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,164 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
+        <v>יהודה בוחבוט - אלף גלגולים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דוד פילס - אהבה יוונית</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409547&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דוד פילס - אהבה יוונית</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אניה בוקשטיין - רק עכשיו</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409546&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אניה בוקשטיין - רק עכשיו</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409545&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אביה שרמן &amp; אביעד - משיח</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409544&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אביה שרמן &amp; אביעד - משיח</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - המונית העצובה</v>
+        <v>איציק קלה &amp; יובל טייב - רפאני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409551&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=383792&amp;sid=adb305d69ff5373f52ea1464f61a4067</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - המונית העצובה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רומי קוגן - מסיבה של מחשבות</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409550&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רומי קוגן - מסיבה של מחשבות</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>משה כורסיה - עומד מולך היום</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409549&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>משה כורסיה - עומד מולך היום</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יהודה בוחבוט - אלף גלגולים</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409548&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יהודה בוחבוט - אלף גלגולים</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דוד פילס - אהבה יוונית</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409547&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דוד פילס - אהבה יוונית</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אניה בוקשטיין - רק עכשיו</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409546&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אניה בוקשטיין - רק עכשיו</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409545&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביה שרמן &amp; אביעד - משיח</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409544&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביה שרמן &amp; אביעד - משיח</v>
+        <v>איציק קלה &amp; יובל טייב - רפאני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איציק קלה &amp; יובל טייב - רפאני</v>
+        <v>חזי פניאן - מתל אביב לטהרן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=383792&amp;sid=adb305d69ff5373f52ea1464f61a4067</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409563&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,430 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איציק קלה &amp; יובל טייב - רפאני</v>
+        <v>חזי פניאן - מתל אביב לטהרן</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409562&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דוד ירושלמי - טעם מר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409561&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דוד ירושלמי - טעם מר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גיל ואזנה - בני (לא) ילד רע</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409560&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גיל ואזנה - בני (לא) ילד רע</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409559&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409558&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409557&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איתמר הרוש - לוקה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409556&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איתמר הרוש - לוקה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409555&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409554&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409553&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אבירם עמר - חץ וסוכריה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409552&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אבירם עמר - חץ וסוכריה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חזי פניאן - מתל אביב לטהרן</v>
+        <v>משה גנון - דרמה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409563&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409567&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חזי פניאן - מתל אביב לטהרן</v>
+        <v>משה גנון - דרמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409562&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409566&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-10</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דוד ירושלמי - טעם מר</v>
+        <v>ליאור ברגר - אם רק תגידי כן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409561&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409565&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-10</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דוד ירושלמי - טעם מר</v>
+        <v>ליאור ברגר - אם רק תגידי כן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל ואזנה - בני (לא) ילד רע</v>
+        <v>חן אלדטוב - לרקוד על הכאב</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409560&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409564&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-10</v>
@@ -583,316 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל ואזנה - בני (לא) ילד רע</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409559&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409558&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409557&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>איתמר הרוש - לוקה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409556&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>איתמר הרוש - לוקה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409555&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409554&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409553&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אבירם עמר - חץ וסוכריה</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409552&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אבירם עמר - חץ וסוכריה</v>
+        <v>חן אלדטוב - לרקוד על הכאב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה גנון - דרמה</v>
+        <v>שיר אוזן - לא להפסיד לך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409567&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409570&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה גנון - דרמה</v>
+        <v>שיר אוזן - לא להפסיד לך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
+        <v>רואי אדם - אהבת חיי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409566&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409569&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-10</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
+        <v>רואי אדם - אהבת חיי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור ברגר - אם רק תגידי כן</v>
+        <v>ניצן אלון - לפני שלושים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409565&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409568&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-10</v>
@@ -545,50 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור ברגר - אם רק תגידי כן</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>חן אלדטוב - לרקוד על הכאב</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409564&amp;sid=fab2598180a774363108ef750cff9054</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>חן אלדטוב - לרקוד על הכאב</v>
+        <v>ניצן אלון - לפני שלושים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אוזן - לא להפסיד לך</v>
+        <v>שירז אברהם - חושך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409570&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409571&amp;sid=107ae0d36c82a37240c0a52fbddafdb6</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אוזן - לא להפסיד לך</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רואי אדם - אהבת חיי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409569&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רואי אדם - אהבת חיי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ניצן אלון - לפני שלושים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409568&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ניצן אלון - לפני שלושים</v>
+        <v>שירז אברהם - חושך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>